--- a/tables/database results/imb all/all.xlsx
+++ b/tables/database results/imb all/all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenne\OneDrive\Bureaublad\bestanden\Regularization-Oversampling-for-Classification-Tasks-To-Exploit-What-You-Do-Not-Know\tables\database results\imb all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenne\OneDrive\Bureaublad\k\BROOD_0112\tables\database results\imb all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEC9CDE-D4C1-4CB0-AF57-A3A5A1F17B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E1A1C6-D7E5-4A52-A0C5-2C2DE2DD8014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17100" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="3276" windowWidth="17100" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,9 +76,6 @@
     <t>german_credit_ROC_AUC.csv</t>
   </si>
   <si>
-    <t>kag_credit_card_approval_ROC_AUC.csv</t>
-  </si>
-  <si>
     <t>kdd_ROC_AUC.csv</t>
   </si>
   <si>
@@ -93,13 +90,16 @@
   <si>
     <t>vub_credit_scoring_ROC_AUC.csv</t>
   </si>
+  <si>
+    <t>credit_card_approval_ROC_AUC.csv</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -159,9 +159,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4">
         <v>0.81668407871196613</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4">
         <v>0.61820583248631444</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4">
         <v>0.77475988430722531</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4">
         <v>0.52762416685077251</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4">
         <v>0.94750305015611758</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>0.98008662943120939</v>
